--- a/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_EA7 EMPORIO ARMANI MILAN.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/aggregate_individual/AGG_IND_EA7 EMPORIO ARMANI MILAN.xlsx
@@ -565,13 +565,13 @@
         <v>26</v>
       </c>
       <c r="D2" t="n">
-        <v>43.2819</v>
+        <v>22.2714</v>
       </c>
       <c r="E2" t="n">
-        <v>46.6268</v>
+        <v>27.9863</v>
       </c>
       <c r="F2" t="n">
-        <v>-3.3448</v>
+        <v>-5.7149</v>
       </c>
       <c r="G2" t="n">
         <v>3.2538</v>
@@ -610,13 +610,13 @@
         <v>35.025</v>
       </c>
       <c r="S2" t="n">
-        <v>33.5223</v>
+        <v>12.5114</v>
       </c>
       <c r="T2" t="n">
-        <v>24.0296</v>
+        <v>5.3889</v>
       </c>
       <c r="U2" t="n">
-        <v>9.492699999999999</v>
+        <v>7.1226</v>
       </c>
       <c r="V2" t="n">
         <v>5.5785</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. DUNSTON</t>
+          <t>A. BROOKS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,70 +640,70 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>17.0636</v>
+        <v>17.5666</v>
       </c>
       <c r="E3" t="n">
-        <v>14.4142</v>
+        <v>24.132</v>
       </c>
       <c r="F3" t="n">
-        <v>2.6497</v>
+        <v>-6.5652</v>
       </c>
       <c r="G3" t="n">
-        <v>6.474699999999999</v>
+        <v>12.0445</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7354999999999998</v>
+        <v>-14.0561</v>
       </c>
       <c r="I3" t="n">
-        <v>5.7388</v>
+        <v>26.1003</v>
       </c>
       <c r="J3" t="n">
-        <v>6.416799999999999</v>
+        <v>52.0046</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3754</v>
+        <v>7.920699999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>3.0413</v>
+        <v>44.0844</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0576</v>
+        <v>-39.9601</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.6399</v>
+        <v>-21.9765</v>
       </c>
       <c r="O3" t="n">
-        <v>2.6976</v>
+        <v>-17.9833</v>
       </c>
       <c r="P3" t="n">
-        <v>8.814399999999999</v>
+        <v>8.118400000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-3.7113</v>
+        <v>-44.3033</v>
       </c>
       <c r="R3" t="n">
-        <v>12.5257</v>
+        <v>52.4217</v>
       </c>
       <c r="S3" t="n">
-        <v>4.0609</v>
+        <v>4.435</v>
       </c>
       <c r="T3" t="n">
-        <v>4.9606</v>
+        <v>-2.5375</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.8997999999999999</v>
+        <v>6.9724</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.2862</v>
+        <v>-7.0315</v>
       </c>
       <c r="W3" t="n">
-        <v>6.7479</v>
+        <v>18.9675</v>
       </c>
       <c r="X3" t="n">
-        <v>-9.0341</v>
+        <v>-25.999</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>13.2207</v>
+        <v>14.5122</v>
       </c>
       <c r="E4" t="n">
-        <v>24.6628</v>
+        <v>27.1122</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.4421</v>
+        <v>-12.5996</v>
       </c>
       <c r="G4" t="n">
         <v>-15.3688</v>
@@ -766,13 +766,13 @@
         <v>44.5349</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1843</v>
+        <v>0.1072000000000003</v>
       </c>
       <c r="T4" t="n">
-        <v>-8.2241</v>
+        <v>-5.7748</v>
       </c>
       <c r="U4" t="n">
-        <v>7.039400000000001</v>
+        <v>5.8822</v>
       </c>
       <c r="V4" t="n">
         <v>21.1915</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. BROOKS</t>
+          <t>B. DUNSTON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="D5" t="n">
-        <v>10.0859</v>
+        <v>13.8677</v>
       </c>
       <c r="E5" t="n">
-        <v>16.8275</v>
+        <v>10.4545</v>
       </c>
       <c r="F5" t="n">
-        <v>-6.7415</v>
+        <v>3.4129</v>
       </c>
       <c r="G5" t="n">
-        <v>12.0445</v>
+        <v>6.474699999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>-14.0561</v>
+        <v>0.7354999999999998</v>
       </c>
       <c r="I5" t="n">
-        <v>26.1003</v>
+        <v>5.7388</v>
       </c>
       <c r="J5" t="n">
-        <v>52.0046</v>
+        <v>6.416799999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>7.920699999999999</v>
+        <v>3.3754</v>
       </c>
       <c r="L5" t="n">
-        <v>44.0844</v>
+        <v>3.0413</v>
       </c>
       <c r="M5" t="n">
-        <v>-39.9601</v>
+        <v>0.0576</v>
       </c>
       <c r="N5" t="n">
-        <v>-21.9765</v>
+        <v>-2.6399</v>
       </c>
       <c r="O5" t="n">
-        <v>-17.9833</v>
+        <v>2.6976</v>
       </c>
       <c r="P5" t="n">
-        <v>8.118400000000001</v>
+        <v>8.814399999999999</v>
       </c>
       <c r="Q5" t="n">
-        <v>-44.3033</v>
+        <v>-3.7113</v>
       </c>
       <c r="R5" t="n">
-        <v>52.4217</v>
+        <v>12.5257</v>
       </c>
       <c r="S5" t="n">
-        <v>-3.0457</v>
+        <v>0.8651000000000002</v>
       </c>
       <c r="T5" t="n">
-        <v>-9.8421</v>
+        <v>1.001</v>
       </c>
       <c r="U5" t="n">
-        <v>6.7965</v>
+        <v>-0.1361000000000001</v>
       </c>
       <c r="V5" t="n">
-        <v>-7.0315</v>
+        <v>-2.2862</v>
       </c>
       <c r="W5" t="n">
-        <v>18.9675</v>
+        <v>6.7479</v>
       </c>
       <c r="X5" t="n">
-        <v>-25.999</v>
+        <v>-9.0341</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. BOLMARO</t>
+          <t>M. GUDURIC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D6" t="n">
-        <v>1.4596</v>
+        <v>8.814999999999998</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4011999999999998</v>
+        <v>17.7042</v>
       </c>
       <c r="F6" t="n">
-        <v>1.860899999999999</v>
+        <v>-8.888400000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1749</v>
+        <v>38.16</v>
       </c>
       <c r="H6" t="n">
-        <v>-6.1684</v>
+        <v>11.778</v>
       </c>
       <c r="I6" t="n">
-        <v>4.993600000000001</v>
+        <v>26.382</v>
       </c>
       <c r="J6" t="n">
-        <v>25.6596</v>
+        <v>70.6604</v>
       </c>
       <c r="K6" t="n">
-        <v>3.083500000000001</v>
+        <v>30.6175</v>
       </c>
       <c r="L6" t="n">
-        <v>22.5766</v>
+        <v>40.0432</v>
       </c>
       <c r="M6" t="n">
-        <v>-26.8346</v>
+        <v>-32.5003</v>
       </c>
       <c r="N6" t="n">
-        <v>-9.2517</v>
+        <v>-18.8396</v>
       </c>
       <c r="O6" t="n">
-        <v>-17.583</v>
+        <v>-13.6614</v>
       </c>
       <c r="P6" t="n">
-        <v>-8.1183</v>
+        <v>-46.1585</v>
       </c>
       <c r="Q6" t="n">
-        <v>-50.7978</v>
+        <v>-92.7809</v>
       </c>
       <c r="R6" t="n">
-        <v>42.6794</v>
+        <v>46.6228</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2534999999999994</v>
+        <v>1.0452</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.8373</v>
+        <v>-5.553900000000001</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5842999999999996</v>
+        <v>6.5991</v>
       </c>
       <c r="V6" t="n">
-        <v>11.0056</v>
+        <v>15.7683</v>
       </c>
       <c r="W6" t="n">
-        <v>25.5736</v>
+        <v>45.3782</v>
       </c>
       <c r="X6" t="n">
-        <v>-14.568</v>
+        <v>-29.6098</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. DIOP</t>
+          <t>L. BOLMARO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3739</v>
+        <v>7.072599999999998</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2444</v>
+        <v>2.425199999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.6182</v>
+        <v>4.647400000000001</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7043999999999999</v>
+        <v>-1.1749</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1224</v>
+        <v>-6.1684</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5821</v>
+        <v>4.993600000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.7191</v>
+        <v>25.6596</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.7191</v>
+        <v>3.083500000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>22.5766</v>
       </c>
       <c r="M7" t="n">
-        <v>0.01469999999999999</v>
+        <v>-26.8346</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5967</v>
+        <v>-9.2517</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.5821</v>
+        <v>-17.583</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9278</v>
+        <v>-8.1183</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-50.7978</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9278</v>
+        <v>42.6794</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9216</v>
+        <v>5.3599</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.5975</v>
+        <v>1.9893</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3241999999999999</v>
+        <v>3.3708</v>
       </c>
       <c r="V7" t="n">
-        <v>1.0722</v>
+        <v>11.0056</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0722</v>
+        <v>25.5736</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-14.568</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. RICCI</t>
+          <t>Q. ELLIS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4075</v>
+        <v>2.869100000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>16.192</v>
+        <v>19.9797</v>
       </c>
       <c r="F8" t="n">
-        <v>-16.599</v>
+        <v>-17.1107</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.3929</v>
+        <v>26.1727</v>
       </c>
       <c r="H8" t="n">
-        <v>0.05689999999999962</v>
+        <v>7.0858</v>
       </c>
       <c r="I8" t="n">
-        <v>-3.4496</v>
+        <v>19.0869</v>
       </c>
       <c r="J8" t="n">
-        <v>23.3124</v>
+        <v>72.1165</v>
       </c>
       <c r="K8" t="n">
-        <v>10.2864</v>
+        <v>27.2097</v>
       </c>
       <c r="L8" t="n">
-        <v>13.0256</v>
+        <v>44.9064</v>
       </c>
       <c r="M8" t="n">
-        <v>-26.7051</v>
+        <v>-45.9436</v>
       </c>
       <c r="N8" t="n">
-        <v>-10.2294</v>
+        <v>-20.1242</v>
       </c>
       <c r="O8" t="n">
-        <v>-16.4759</v>
+        <v>-25.8199</v>
       </c>
       <c r="P8" t="n">
-        <v>28.5307</v>
+        <v>-21.1077</v>
       </c>
       <c r="Q8" t="n">
-        <v>-11.1341</v>
+        <v>-74.6891</v>
       </c>
       <c r="R8" t="n">
-        <v>39.6643</v>
+        <v>53.5811</v>
       </c>
       <c r="S8" t="n">
-        <v>4.428</v>
+        <v>-4.6549</v>
       </c>
       <c r="T8" t="n">
-        <v>2.798999999999999</v>
+        <v>-3.9521</v>
       </c>
       <c r="U8" t="n">
-        <v>1.629</v>
+        <v>-0.7026999999999999</v>
       </c>
       <c r="V8" t="n">
-        <v>-29.9731</v>
+        <v>2.4591</v>
       </c>
       <c r="W8" t="n">
-        <v>1.214</v>
+        <v>26.504</v>
       </c>
       <c r="X8" t="n">
-        <v>-31.1871</v>
+        <v>-24.0449</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. TOTE</t>
+          <t>S. SHIELDS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,76 +1108,76 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4452</v>
+        <v>2.772699999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>1.1609</v>
+        <v>12.4654</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6061</v>
+        <v>-9.692500000000001</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.5233</v>
+        <v>-4.987699999999998</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5942</v>
+        <v>-10.2918</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.1175</v>
+        <v>5.304400000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>1.8144</v>
+        <v>45.419</v>
       </c>
       <c r="K9" t="n">
-        <v>1.6672</v>
+        <v>14.4986</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1472</v>
+        <v>30.9197</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3377</v>
+        <v>-50.4063</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.073</v>
+        <v>-24.7909</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2647</v>
+        <v>-25.6155</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.232</v>
+        <v>-5.5667</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-62.1635</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9278</v>
+        <v>56.5966</v>
       </c>
       <c r="S9" t="n">
-        <v>0.8461</v>
+        <v>-6.162599999999999</v>
       </c>
       <c r="T9" t="n">
-        <v>0.9006</v>
+        <v>-8.268600000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0545</v>
+        <v>2.1058</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5361</v>
+        <v>19.4899</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3943</v>
+        <v>37.4785</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1418</v>
+        <v>-17.9886</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. CANCAR</t>
+          <t>O. DIOP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2508</v>
+        <v>0.4246</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9588</v>
+        <v>-0.1264</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7079</v>
+        <v>0.5509999999999999</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4779</v>
+        <v>-0.7043999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.749</v>
+        <v>-0.1224</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2711</v>
+        <v>-0.5821</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.431</v>
+        <v>-0.7191</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6519</v>
+        <v>-0.7191</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2208</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.04670000000000002</v>
+        <v>0.01469999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.09700000000000003</v>
+        <v>0.5967</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0503</v>
+        <v>-0.5821</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3196</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6133000000000001</v>
+        <v>-0.8709</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2082</v>
+        <v>-0.4795</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4051</v>
+        <v>-0.3914</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. TONUT</t>
+          <t>G. RICCI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1264,76 +1264,76 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1112</v>
+        <v>-0.509399999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>0.02960000000000029</v>
+        <v>14.9648</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.1406</v>
+        <v>-15.4742</v>
       </c>
       <c r="G11" t="n">
-        <v>-2.9239</v>
+        <v>-3.3929</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.3882</v>
+        <v>0.05689999999999962</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.5356</v>
+        <v>-3.4496</v>
       </c>
       <c r="J11" t="n">
-        <v>1.4919</v>
+        <v>23.3124</v>
       </c>
       <c r="K11" t="n">
-        <v>2.1713</v>
+        <v>10.2864</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6794</v>
+        <v>13.0256</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.4157</v>
+        <v>-26.7051</v>
       </c>
       <c r="N11" t="n">
-        <v>-3.5595</v>
+        <v>-10.2294</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8561999999999999</v>
+        <v>-16.4759</v>
       </c>
       <c r="P11" t="n">
-        <v>4.8711</v>
+        <v>28.5307</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.6238</v>
+        <v>-11.1341</v>
       </c>
       <c r="R11" t="n">
-        <v>6.4948</v>
+        <v>39.6643</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.0942</v>
+        <v>4.326000000000001</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0525</v>
+        <v>1.571899999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.0416</v>
+        <v>2.7541</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.9641</v>
+        <v>-29.9731</v>
       </c>
       <c r="W11" t="n">
         <v>1.214</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.1781</v>
+        <v>-31.1871</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>N. SESTINA</t>
+          <t>L. TOTE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.223500000000001</v>
+        <v>-1.1694</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.7359</v>
+        <v>0.5711000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.4877</v>
+        <v>-1.7405</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.0056</v>
+        <v>-0.5233</v>
       </c>
       <c r="H12" t="n">
-        <v>4.22</v>
+        <v>0.5942</v>
       </c>
       <c r="I12" t="n">
-        <v>-10.2256</v>
+        <v>-1.1175</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7659</v>
+        <v>1.8144</v>
       </c>
       <c r="K12" t="n">
-        <v>6.288600000000001</v>
+        <v>1.6672</v>
       </c>
       <c r="L12" t="n">
-        <v>-8.054500000000001</v>
+        <v>0.1472</v>
       </c>
       <c r="M12" t="n">
-        <v>-4.2397</v>
+        <v>-2.3377</v>
       </c>
       <c r="N12" t="n">
-        <v>-2.0685</v>
+        <v>-1.073</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.1711</v>
+        <v>-1.2647</v>
       </c>
       <c r="P12" t="n">
-        <v>5.798999999999999</v>
+        <v>-0.232</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R12" t="n">
-        <v>5.798999999999999</v>
+        <v>0.9278</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5886000000000001</v>
+        <v>0.1219</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.04220000000000002</v>
+        <v>0.3108</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5465</v>
+        <v>-0.1889</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.428</v>
+        <v>-0.5361</v>
       </c>
       <c r="W12" t="n">
-        <v>1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="X12" t="n">
-        <v>-3.5002</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. FLACCADORI</t>
+          <t>V. CANCAR</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.3378</v>
+        <v>-1.6396</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.6658</v>
+        <v>-2.8408</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.6721</v>
+        <v>1.2012</v>
       </c>
       <c r="G13" t="n">
-        <v>1.2739</v>
+        <v>-0.4779</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7350000000000001</v>
+        <v>-0.749</v>
       </c>
       <c r="I13" t="n">
-        <v>0.5389999999999999</v>
+        <v>0.2711</v>
       </c>
       <c r="J13" t="n">
-        <v>2.0387</v>
+        <v>-0.431</v>
       </c>
       <c r="K13" t="n">
-        <v>0.9613999999999998</v>
+        <v>-0.6519</v>
       </c>
       <c r="L13" t="n">
-        <v>1.0774</v>
+        <v>0.2208</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.7646999999999999</v>
+        <v>-0.04670000000000002</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.2263000000000001</v>
+        <v>-0.09700000000000003</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.5383</v>
+        <v>0.0503</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.4792</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q13" t="n">
-        <v>-6.0309</v>
+        <v>-2.3196</v>
       </c>
       <c r="R13" t="n">
-        <v>2.5516</v>
+        <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>-2.9495</v>
+        <v>-0.001899999999999985</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.6351</v>
+        <v>-0.09019999999999997</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.3144</v>
+        <v>0.08829999999999999</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.1829</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>0.9615</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1444</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. GUDURIC</t>
+          <t>N. SESTINA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>-7.791699999999998</v>
+        <v>-1.6833</v>
       </c>
       <c r="E14" t="n">
-        <v>4.757099999999999</v>
+        <v>0.1090999999999998</v>
       </c>
       <c r="F14" t="n">
-        <v>-12.5486</v>
+        <v>-1.7926</v>
       </c>
       <c r="G14" t="n">
-        <v>38.16</v>
+        <v>-6.0056</v>
       </c>
       <c r="H14" t="n">
-        <v>11.778</v>
+        <v>4.22</v>
       </c>
       <c r="I14" t="n">
-        <v>26.382</v>
+        <v>-10.2256</v>
       </c>
       <c r="J14" t="n">
-        <v>70.6604</v>
+        <v>-1.7659</v>
       </c>
       <c r="K14" t="n">
-        <v>30.6175</v>
+        <v>6.288600000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>40.0432</v>
+        <v>-8.054500000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>-32.5003</v>
+        <v>-4.2397</v>
       </c>
       <c r="N14" t="n">
-        <v>-18.8396</v>
+        <v>-2.0685</v>
       </c>
       <c r="O14" t="n">
-        <v>-13.6614</v>
+        <v>-2.1711</v>
       </c>
       <c r="P14" t="n">
-        <v>-46.1585</v>
+        <v>5.798999999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>-92.7809</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>46.6228</v>
+        <v>5.798999999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>-15.5618</v>
+        <v>0.9513</v>
       </c>
       <c r="T14" t="n">
-        <v>-18.5008</v>
+        <v>0.803</v>
       </c>
       <c r="U14" t="n">
-        <v>2.939</v>
+        <v>0.1485</v>
       </c>
       <c r="V14" t="n">
-        <v>15.7683</v>
+        <v>-2.428</v>
       </c>
       <c r="W14" t="n">
-        <v>45.3782</v>
+        <v>1.0722</v>
       </c>
       <c r="X14" t="n">
-        <v>-29.6098</v>
+        <v>-3.5002</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Q. ELLIS</t>
+          <t>S. TONUT</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,70 +1576,70 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>-8.139600000000002</v>
+        <v>-1.8198</v>
       </c>
       <c r="E15" t="n">
-        <v>15.474</v>
+        <v>1.1973</v>
       </c>
       <c r="F15" t="n">
-        <v>-23.6141</v>
+        <v>-3.0172</v>
       </c>
       <c r="G15" t="n">
-        <v>26.1727</v>
+        <v>-2.9239</v>
       </c>
       <c r="H15" t="n">
-        <v>7.0858</v>
+        <v>-1.3882</v>
       </c>
       <c r="I15" t="n">
-        <v>19.0869</v>
+        <v>-1.5356</v>
       </c>
       <c r="J15" t="n">
-        <v>72.1165</v>
+        <v>1.4919</v>
       </c>
       <c r="K15" t="n">
-        <v>27.2097</v>
+        <v>2.1713</v>
       </c>
       <c r="L15" t="n">
-        <v>44.9064</v>
+        <v>-0.6794</v>
       </c>
       <c r="M15" t="n">
-        <v>-45.9436</v>
+        <v>-4.4157</v>
       </c>
       <c r="N15" t="n">
-        <v>-20.1242</v>
+        <v>-3.5595</v>
       </c>
       <c r="O15" t="n">
-        <v>-25.8199</v>
+        <v>-0.8561999999999999</v>
       </c>
       <c r="P15" t="n">
-        <v>-21.1077</v>
+        <v>4.8711</v>
       </c>
       <c r="Q15" t="n">
-        <v>-74.6891</v>
+        <v>-1.6238</v>
       </c>
       <c r="R15" t="n">
-        <v>53.5811</v>
+        <v>6.4948</v>
       </c>
       <c r="S15" t="n">
-        <v>-15.6637</v>
+        <v>-0.8031000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-8.4579</v>
+        <v>0.1151</v>
       </c>
       <c r="U15" t="n">
-        <v>-7.2061</v>
+        <v>-0.9178000000000002</v>
       </c>
       <c r="V15" t="n">
-        <v>2.4591</v>
+        <v>-2.9641</v>
       </c>
       <c r="W15" t="n">
-        <v>26.504</v>
+        <v>1.214</v>
       </c>
       <c r="X15" t="n">
-        <v>-24.0449</v>
+        <v>-4.1781</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>-8.906899999999998</v>
+        <v>-4.612300000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>-9.004899999999999</v>
+        <v>-5.5962</v>
       </c>
       <c r="F16" t="n">
-        <v>0.09810000000000008</v>
+        <v>0.9840999999999998</v>
       </c>
       <c r="G16" t="n">
         <v>1.5731</v>
@@ -1702,13 +1702,13 @@
         <v>11.5979</v>
       </c>
       <c r="S16" t="n">
-        <v>-3.3461</v>
+        <v>0.9484</v>
       </c>
       <c r="T16" t="n">
-        <v>-4.1815</v>
+        <v>-0.7724</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8351000000000002</v>
+        <v>1.721</v>
       </c>
       <c r="V16" t="n">
         <v>-1.1033</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. BOOKER</t>
+          <t>D. FLACCADORI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>-9.146800000000001</v>
+        <v>-5.3208</v>
       </c>
       <c r="E17" t="n">
-        <v>12.3549</v>
+        <v>-4.1192</v>
       </c>
       <c r="F17" t="n">
-        <v>-21.5014</v>
+        <v>-1.2015</v>
       </c>
       <c r="G17" t="n">
-        <v>-25.577</v>
+        <v>1.2739</v>
       </c>
       <c r="H17" t="n">
-        <v>-8.082799999999999</v>
+        <v>0.7350000000000001</v>
       </c>
       <c r="I17" t="n">
-        <v>-17.4947</v>
+        <v>0.5389999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>11.3706</v>
+        <v>2.0387</v>
       </c>
       <c r="K17" t="n">
-        <v>7.748900000000001</v>
+        <v>0.9613999999999998</v>
       </c>
       <c r="L17" t="n">
-        <v>3.6215</v>
+        <v>1.0774</v>
       </c>
       <c r="M17" t="n">
-        <v>-36.9477</v>
+        <v>-0.7646999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-15.8315</v>
+        <v>-0.2263000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>-21.1162</v>
+        <v>-0.5383</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9279999999999997</v>
+        <v>-3.4792</v>
       </c>
       <c r="Q17" t="n">
-        <v>-42.2157</v>
+        <v>-6.0309</v>
       </c>
       <c r="R17" t="n">
-        <v>43.1435</v>
+        <v>2.5516</v>
       </c>
       <c r="S17" t="n">
-        <v>14.8736</v>
+        <v>-1.9326</v>
       </c>
       <c r="T17" t="n">
-        <v>16.0976</v>
+        <v>-1.0886</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.2241</v>
+        <v>-0.8439</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6294000000000002</v>
+        <v>-1.1829</v>
       </c>
       <c r="W17" t="n">
-        <v>27.1022</v>
+        <v>0.9615</v>
       </c>
       <c r="X17" t="n">
-        <v>-26.4729</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. SHIELDS</t>
+          <t>D. BOOKER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,70 +1810,70 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D18" t="n">
-        <v>-11.806</v>
+        <v>-19.9405</v>
       </c>
       <c r="E18" t="n">
-        <v>3.721500000000001</v>
+        <v>-1.0333</v>
       </c>
       <c r="F18" t="n">
-        <v>-15.5279</v>
+        <v>-18.9072</v>
       </c>
       <c r="G18" t="n">
-        <v>-4.987699999999998</v>
+        <v>-25.577</v>
       </c>
       <c r="H18" t="n">
-        <v>-10.2918</v>
+        <v>-8.082799999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>5.304400000000001</v>
+        <v>-17.4947</v>
       </c>
       <c r="J18" t="n">
-        <v>45.419</v>
+        <v>11.3706</v>
       </c>
       <c r="K18" t="n">
-        <v>14.4986</v>
+        <v>7.748900000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>30.9197</v>
+        <v>3.6215</v>
       </c>
       <c r="M18" t="n">
-        <v>-50.4063</v>
+        <v>-36.9477</v>
       </c>
       <c r="N18" t="n">
-        <v>-24.7909</v>
+        <v>-15.8315</v>
       </c>
       <c r="O18" t="n">
-        <v>-25.6155</v>
+        <v>-21.1162</v>
       </c>
       <c r="P18" t="n">
-        <v>-5.5667</v>
+        <v>0.9279999999999997</v>
       </c>
       <c r="Q18" t="n">
-        <v>-62.1635</v>
+        <v>-42.2157</v>
       </c>
       <c r="R18" t="n">
-        <v>56.5966</v>
+        <v>43.1435</v>
       </c>
       <c r="S18" t="n">
-        <v>-20.742</v>
+        <v>4.0797</v>
       </c>
       <c r="T18" t="n">
-        <v>-17.0128</v>
+        <v>2.7095</v>
       </c>
       <c r="U18" t="n">
-        <v>-3.7296</v>
+        <v>1.3701</v>
       </c>
       <c r="V18" t="n">
-        <v>19.4899</v>
+        <v>0.6294000000000002</v>
       </c>
       <c r="W18" t="n">
-        <v>37.4785</v>
+        <v>27.1022</v>
       </c>
       <c r="X18" t="n">
-        <v>-17.9886</v>
+        <v>-26.4729</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>22</v>
       </c>
       <c r="D19" t="n">
-        <v>-32.491</v>
+        <v>-23.4044</v>
       </c>
       <c r="E19" t="n">
-        <v>-27.593</v>
+        <v>-22.0731</v>
       </c>
       <c r="F19" t="n">
-        <v>-4.8978</v>
+        <v>-1.3314</v>
       </c>
       <c r="G19" t="n">
         <v>-2.6608</v>
@@ -1936,13 +1936,13 @@
         <v>15.7732</v>
       </c>
       <c r="S19" t="n">
-        <v>-11.8224</v>
+        <v>-2.7362</v>
       </c>
       <c r="T19" t="n">
-        <v>-7.6087</v>
+        <v>-2.0886</v>
       </c>
       <c r="U19" t="n">
-        <v>-4.2138</v>
+        <v>-0.6474000000000002</v>
       </c>
       <c r="V19" t="n">
         <v>-5.2503</v>
@@ -1969,13 +1969,13 @@
         <v>38</v>
       </c>
       <c r="D20" t="n">
-        <v>-8.572399999999988</v>
+        <v>30.07240000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>110.6173</v>
+        <v>123.3128</v>
       </c>
       <c r="F20" t="n">
-        <v>-119.1889</v>
+        <v>-93.2393</v>
       </c>
       <c r="G20" t="n">
         <v>25.1555</v>
@@ -1987,7 +1987,7 @@
         <v>55.22369999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>389.0781</v>
+        <v>389.0781000000001</v>
       </c>
       <c r="K20" t="n">
         <v>145.7972</v>
@@ -1996,7 +1996,7 @@
         <v>243.2792</v>
       </c>
       <c r="M20" t="n">
-        <v>-363.9219</v>
+        <v>-363.9219000000001</v>
       </c>
       <c r="N20" t="n">
         <v>-175.8659</v>
@@ -2008,22 +2008,22 @@
         <v>-37.1112</v>
       </c>
       <c r="Q20" t="n">
-        <v>-509.1393</v>
+        <v>-509.1392999999999</v>
       </c>
       <c r="R20" t="n">
         <v>472.0269</v>
       </c>
       <c r="S20" t="n">
-        <v>-21.0558</v>
+        <v>17.5889</v>
       </c>
       <c r="T20" t="n">
-        <v>-29.4133</v>
+        <v>-16.7167</v>
       </c>
       <c r="U20" t="n">
-        <v>8.356300000000001</v>
+        <v>34.30670000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>24.439</v>
+        <v>24.43899999999999</v>
       </c>
       <c r="W20" t="n">
         <v>260.0866</v>
